--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/142.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/142.xlsx
@@ -426,13 +426,13 @@
         <v>-4.054978023505462</v>
       </c>
       <c r="E2">
-        <v>-15.81264988548916</v>
+        <v>-15.06629397038898</v>
       </c>
       <c r="F2">
-        <v>-0.8339283804220065</v>
+        <v>0.399553757451403</v>
       </c>
       <c r="G2">
-        <v>-6.930502436402072</v>
+        <v>-8.487008390419049</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.805205156247925</v>
       </c>
       <c r="E3">
-        <v>-15.57151770152873</v>
+        <v>-14.63757427913481</v>
       </c>
       <c r="F3">
-        <v>-0.6396000146644648</v>
+        <v>0.433660128526867</v>
       </c>
       <c r="G3">
-        <v>-7.226187121787617</v>
+        <v>-8.737133348093144</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.500959256288858</v>
       </c>
       <c r="E4">
-        <v>-16.84220750808104</v>
+        <v>-14.54173365523648</v>
       </c>
       <c r="F4">
-        <v>-0.6601261305384338</v>
+        <v>0.8824820128746812</v>
       </c>
       <c r="G4">
-        <v>-6.776383299366841</v>
+        <v>-8.984950855526368</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.173417702246235</v>
       </c>
       <c r="E5">
-        <v>-17.46363188225761</v>
+        <v>-17.69974651701754</v>
       </c>
       <c r="F5">
-        <v>-0.2213738803390504</v>
+        <v>0.5204092480502397</v>
       </c>
       <c r="G5">
-        <v>-6.786003744703963</v>
+        <v>-9.23200031639448</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.819086271389869</v>
       </c>
       <c r="E6">
-        <v>-18.58538923564565</v>
+        <v>-18.12419585728247</v>
       </c>
       <c r="F6">
-        <v>-0.401328414923215</v>
+        <v>0.7967708377070163</v>
       </c>
       <c r="G6">
-        <v>-6.450546165209613</v>
+        <v>-8.815901158109023</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.442139572965689</v>
       </c>
       <c r="E7">
-        <v>-18.51742136926452</v>
+        <v>-18.27055160873637</v>
       </c>
       <c r="F7">
-        <v>-0.2065229095416609</v>
+        <v>0.6869616264245111</v>
       </c>
       <c r="G7">
-        <v>-6.060792328325677</v>
+        <v>-7.56771624180099</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.041160379452046</v>
       </c>
       <c r="E8">
-        <v>-19.50060288954384</v>
+        <v>-19.49518230615666</v>
       </c>
       <c r="F8">
-        <v>-0.2491399273134871</v>
+        <v>0.8222978075916859</v>
       </c>
       <c r="G8">
-        <v>-6.389168650911525</v>
+        <v>-8.378256969453989</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.613396468101481</v>
       </c>
       <c r="E9">
-        <v>-19.98968713932026</v>
+        <v>-20.07655232773539</v>
       </c>
       <c r="F9">
-        <v>0.2986950559561464</v>
+        <v>1.259433912988207</v>
       </c>
       <c r="G9">
-        <v>-6.091444669473789</v>
+        <v>-7.425872607625377</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.160632632933079</v>
       </c>
       <c r="E10">
-        <v>-21.19342798614316</v>
+        <v>-21.05049576103906</v>
       </c>
       <c r="F10">
-        <v>0.06565459636357546</v>
+        <v>1.704560450352133</v>
       </c>
       <c r="G10">
-        <v>-6.07173037078743</v>
+        <v>-6.536600485957429</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.6849128136978753</v>
       </c>
       <c r="E11">
-        <v>-21.87211944262073</v>
+        <v>-21.7238572036096</v>
       </c>
       <c r="F11">
-        <v>0.06554608023380873</v>
+        <v>1.315335458798729</v>
       </c>
       <c r="G11">
-        <v>-5.133468796229347</v>
+        <v>-6.413335633348205</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.1956804477202218</v>
       </c>
       <c r="E12">
-        <v>-21.54791240298958</v>
+        <v>-21.6491736102751</v>
       </c>
       <c r="F12">
-        <v>-0.01530174991202022</v>
+        <v>1.828442795440799</v>
       </c>
       <c r="G12">
-        <v>-4.799438061862423</v>
+        <v>-5.60322527661531</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.3010871788242787</v>
       </c>
       <c r="E13">
-        <v>-23.82799906585161</v>
+        <v>-22.89614326997523</v>
       </c>
       <c r="F13">
-        <v>0.3316723622615947</v>
+        <v>1.689011994201586</v>
       </c>
       <c r="G13">
-        <v>-4.522378505680818</v>
+        <v>-5.166964895995693</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.7999509843993684</v>
       </c>
       <c r="E14">
-        <v>-25.48724552768405</v>
+        <v>-23.05411002878479</v>
       </c>
       <c r="F14">
-        <v>0.6541847850305402</v>
+        <v>1.542115945928344</v>
       </c>
       <c r="G14">
-        <v>-4.090229822620975</v>
+        <v>-5.580912199680623</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.299478564666149</v>
       </c>
       <c r="E15">
-        <v>-25.04648009556948</v>
+        <v>-25.71117403888935</v>
       </c>
       <c r="F15">
-        <v>1.05966814359869</v>
+        <v>2.087662150064043</v>
       </c>
       <c r="G15">
-        <v>-3.833103061131321</v>
+        <v>-4.521855439485613</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.803221391398521</v>
       </c>
       <c r="E16">
-        <v>-26.72811986136985</v>
+        <v>-25.95653581757294</v>
       </c>
       <c r="F16">
-        <v>1.008965431608138</v>
+        <v>2.55078579762119</v>
       </c>
       <c r="G16">
-        <v>-3.36096960904816</v>
+        <v>-4.33880544498269</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.307220470898361</v>
       </c>
       <c r="E17">
-        <v>-26.99380543139987</v>
+        <v>-26.53310112822953</v>
       </c>
       <c r="F17">
-        <v>1.033930768393709</v>
+        <v>2.672648582981831</v>
       </c>
       <c r="G17">
-        <v>-2.660742879854755</v>
+        <v>-3.591327299307268</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.80648900849989</v>
       </c>
       <c r="E18">
-        <v>-28.0226294412025</v>
+        <v>-28.15378310541265</v>
       </c>
       <c r="F18">
-        <v>1.070688743525534</v>
+        <v>2.391215728085116</v>
       </c>
       <c r="G18">
-        <v>-1.581978442064463</v>
+        <v>-1.992135171106928</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.282728262894125</v>
       </c>
       <c r="E19">
-        <v>-30.08605579364155</v>
+        <v>-28.08891724372678</v>
       </c>
       <c r="F19">
-        <v>1.295267430098508</v>
+        <v>2.975834365876061</v>
       </c>
       <c r="G19">
-        <v>-3.125569957932743</v>
+        <v>-2.655647950269816</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.716202614147521</v>
       </c>
       <c r="E20">
-        <v>-29.38957649126185</v>
+        <v>-28.30049207783915</v>
       </c>
       <c r="F20">
-        <v>1.253144947666154</v>
+        <v>3.062453431717195</v>
       </c>
       <c r="G20">
-        <v>-2.368335634553087</v>
+        <v>-1.944284545882302</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.080715152844775</v>
       </c>
       <c r="E21">
-        <v>-29.25403020726426</v>
+        <v>-29.74092041138395</v>
       </c>
       <c r="F21">
-        <v>1.678200142860247</v>
+        <v>3.426426471363658</v>
       </c>
       <c r="G21">
-        <v>-1.094338394675357</v>
+        <v>-2.709990555296953</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.354971871067419</v>
       </c>
       <c r="E22">
-        <v>-30.71406909749928</v>
+        <v>-30.03661844289981</v>
       </c>
       <c r="F22">
-        <v>1.664112926808239</v>
+        <v>3.320100545009925</v>
       </c>
       <c r="G22">
-        <v>-1.293067132852267</v>
+        <v>-1.613484903961707</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.523708054800729</v>
       </c>
       <c r="E23">
-        <v>-30.82013048723293</v>
+        <v>-30.09638750709005</v>
       </c>
       <c r="F23">
-        <v>1.850457487537599</v>
+        <v>3.178154820335813</v>
       </c>
       <c r="G23">
-        <v>-0.9776747698714402</v>
+        <v>-1.941149459256612</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.581949565057134</v>
       </c>
       <c r="E24">
-        <v>-32.08352945063288</v>
+        <v>-30.81023577152617</v>
       </c>
       <c r="F24">
-        <v>1.906090642309614</v>
+        <v>2.838401586812401</v>
       </c>
       <c r="G24">
-        <v>-1.077166594963157</v>
+        <v>-1.439217786774472</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.538397327464924</v>
       </c>
       <c r="E25">
-        <v>-31.31864754836732</v>
+        <v>-31.1785954327321</v>
       </c>
       <c r="F25">
-        <v>1.717693387156116</v>
+        <v>3.412844559427358</v>
       </c>
       <c r="G25">
-        <v>-0.7119174161609063</v>
+        <v>-0.6290544613129485</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.408591820282654</v>
       </c>
       <c r="E26">
-        <v>-32.47811803329124</v>
+        <v>-31.85688385502299</v>
       </c>
       <c r="F26">
-        <v>1.905374932873595</v>
+        <v>2.77066432755068</v>
       </c>
       <c r="G26">
-        <v>-0.5383653768101536</v>
+        <v>-1.71385733416687</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.219466864109918</v>
       </c>
       <c r="E27">
-        <v>-31.6340829338456</v>
+        <v>-31.14850372295113</v>
       </c>
       <c r="F27">
-        <v>2.026386156544158</v>
+        <v>3.025359139419832</v>
       </c>
       <c r="G27">
-        <v>-0.9589503243013223</v>
+        <v>-1.021400455354134</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.996300632603955</v>
       </c>
       <c r="E28">
-        <v>-30.77572879958772</v>
+        <v>-31.93350110675876</v>
       </c>
       <c r="F28">
-        <v>1.527316333909928</v>
+        <v>3.179622687373573</v>
       </c>
       <c r="G28">
-        <v>-0.5863053867643396</v>
+        <v>-0.9300327090157885</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.765879667679922</v>
       </c>
       <c r="E29">
-        <v>-30.71435665559877</v>
+        <v>-31.34941400077543</v>
       </c>
       <c r="F29">
-        <v>1.367433141495596</v>
+        <v>2.961019843244395</v>
       </c>
       <c r="G29">
-        <v>-0.9334558131033949</v>
+        <v>-1.100462903923008</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.546139218186568</v>
       </c>
       <c r="E30">
-        <v>-30.41705328004719</v>
+        <v>-30.33902088018402</v>
       </c>
       <c r="F30">
-        <v>1.297424498815398</v>
+        <v>2.82418348871075</v>
       </c>
       <c r="G30">
-        <v>-0.9662732510341902</v>
+        <v>-1.592164990688801</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.348008721782886</v>
       </c>
       <c r="E31">
-        <v>-30.1088204324781</v>
+        <v>-30.51657781755077</v>
       </c>
       <c r="F31">
-        <v>1.638965349194051</v>
+        <v>3.065717199284224</v>
       </c>
       <c r="G31">
-        <v>-1.280947225632995</v>
+        <v>-2.119160803448763</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.176694833956098</v>
       </c>
       <c r="E32">
-        <v>-29.82693198244864</v>
+        <v>-30.58986890512791</v>
       </c>
       <c r="F32">
-        <v>1.436096515513647</v>
+        <v>2.681389515816171</v>
       </c>
       <c r="G32">
-        <v>-1.646739333903686</v>
+        <v>-2.636956610155091</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.029440900728398</v>
       </c>
       <c r="E33">
-        <v>-30.14121260705497</v>
+        <v>-29.951718612204</v>
       </c>
       <c r="F33">
-        <v>1.549965555437272</v>
+        <v>2.634913134314703</v>
       </c>
       <c r="G33">
-        <v>-1.204506729131223</v>
+        <v>-2.313797707339134</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.905207583347247</v>
       </c>
       <c r="E34">
-        <v>-29.71952110746071</v>
+        <v>-29.14732577422152</v>
       </c>
       <c r="F34">
-        <v>1.570389782120697</v>
+        <v>2.469335744373526</v>
       </c>
       <c r="G34">
-        <v>-1.581687114057007</v>
+        <v>-2.502478939804356</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.794404950139105</v>
       </c>
       <c r="E35">
-        <v>-29.31885531268406</v>
+        <v>-28.57614029068604</v>
       </c>
       <c r="F35">
-        <v>1.48050860544734</v>
+        <v>2.856890747242886</v>
       </c>
       <c r="G35">
-        <v>-1.890584186689784</v>
+        <v>-3.02197305637233</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.69370084161339</v>
       </c>
       <c r="E36">
-        <v>-27.95114295051742</v>
+        <v>-28.26478053181466</v>
       </c>
       <c r="F36">
-        <v>1.687529216550575</v>
+        <v>3.033659380795884</v>
       </c>
       <c r="G36">
-        <v>-2.994055225839656</v>
+        <v>-2.244302735378753</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.592699628956556</v>
       </c>
       <c r="E37">
-        <v>-27.47907670606183</v>
+        <v>-28.21448729948547</v>
       </c>
       <c r="F37">
-        <v>1.693054427127248</v>
+        <v>2.751036990308748</v>
       </c>
       <c r="G37">
-        <v>-2.226114598185998</v>
+        <v>-2.838128530939983</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.487922410753963</v>
       </c>
       <c r="E38">
-        <v>-26.95956563942788</v>
+        <v>-27.41631658478953</v>
       </c>
       <c r="F38">
-        <v>1.544140475860786</v>
+        <v>3.075897834664631</v>
       </c>
       <c r="G38">
-        <v>-2.75951300601891</v>
+        <v>-2.603493615844138</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.373263959759077</v>
       </c>
       <c r="E39">
-        <v>-25.20398042155626</v>
+        <v>-27.03515945603792</v>
       </c>
       <c r="F39">
-        <v>2.071578568571288</v>
+        <v>3.153832296654814</v>
       </c>
       <c r="G39">
-        <v>-2.635728397760022</v>
+        <v>-2.517260525637202</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.247615032517559</v>
       </c>
       <c r="E40">
-        <v>-25.55275443267901</v>
+        <v>-26.22876956101805</v>
       </c>
       <c r="F40">
-        <v>2.225361663431404</v>
+        <v>3.143058550214003</v>
       </c>
       <c r="G40">
-        <v>-2.975880330829058</v>
+        <v>-3.335683662219207</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.110745595680996</v>
       </c>
       <c r="E41">
-        <v>-26.30040096287138</v>
+        <v>-25.61355372470599</v>
       </c>
       <c r="F41">
-        <v>2.021092888840269</v>
+        <v>2.925240998382679</v>
       </c>
       <c r="G41">
-        <v>-3.635665435714726</v>
+        <v>-3.627067948949239</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.964220089954857</v>
       </c>
       <c r="E42">
-        <v>-23.87091994249631</v>
+        <v>-25.00139460834912</v>
       </c>
       <c r="F42">
-        <v>2.180513852243839</v>
+        <v>3.512734071061339</v>
       </c>
       <c r="G42">
-        <v>-2.933521900654083</v>
+        <v>-3.797700087134355</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.812736408676257</v>
       </c>
       <c r="E43">
-        <v>-24.12456430013994</v>
+        <v>-24.97008473906008</v>
       </c>
       <c r="F43">
-        <v>2.37638960830981</v>
+        <v>3.447317897262262</v>
       </c>
       <c r="G43">
-        <v>-3.863381310633495</v>
+        <v>-3.378346662583795</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.659028120682979</v>
       </c>
       <c r="E44">
-        <v>-24.13016602248742</v>
+        <v>-23.67716012513012</v>
       </c>
       <c r="F44">
-        <v>2.180561897553202</v>
+        <v>3.511186680752909</v>
       </c>
       <c r="G44">
-        <v>-3.495119535390507</v>
+        <v>-4.037989414011276</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.508612187318253</v>
       </c>
       <c r="E45">
-        <v>-23.27880838057139</v>
+        <v>-22.96135329568568</v>
       </c>
       <c r="F45">
-        <v>2.312444615018105</v>
+        <v>3.472975749196574</v>
       </c>
       <c r="G45">
-        <v>-3.558665457016818</v>
+        <v>-3.470734056948236</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.361715601311532</v>
       </c>
       <c r="E46">
-        <v>-21.92324591416733</v>
+        <v>-22.42249658809096</v>
       </c>
       <c r="F46">
-        <v>2.487920995422736</v>
+        <v>3.613458577037342</v>
       </c>
       <c r="G46">
-        <v>-3.783213139854504</v>
+        <v>-3.798779324980157</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.220392400334372</v>
       </c>
       <c r="E47">
-        <v>-22.64855348207986</v>
+        <v>-20.87981757568996</v>
       </c>
       <c r="F47">
-        <v>2.51631080305148</v>
+        <v>3.800169276158739</v>
       </c>
       <c r="G47">
-        <v>-3.413594040940415</v>
+        <v>-3.476514269459803</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.081352084466104</v>
       </c>
       <c r="E48">
-        <v>-20.70020018264973</v>
+        <v>-21.86851024883662</v>
       </c>
       <c r="F48">
-        <v>2.655418541003602</v>
+        <v>3.717811332237607</v>
       </c>
       <c r="G48">
-        <v>-4.039316942772523</v>
+        <v>-3.811197181297963</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.9422067419519491</v>
       </c>
       <c r="E49">
-        <v>-20.1389637565091</v>
+        <v>-20.14986832191957</v>
       </c>
       <c r="F49">
-        <v>2.49169503730989</v>
+        <v>4.219687663632521</v>
       </c>
       <c r="G49">
-        <v>-3.582372273623539</v>
+        <v>-4.153997550798416</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.7992262133614939</v>
       </c>
       <c r="E50">
-        <v>-18.68429110797317</v>
+        <v>-20.13421791574906</v>
       </c>
       <c r="F50">
-        <v>3.010730171086393</v>
+        <v>3.818684944346113</v>
       </c>
       <c r="G50">
-        <v>-4.306136981601163</v>
+        <v>-4.007287414680074</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.6490027394778741</v>
       </c>
       <c r="E51">
-        <v>-18.87609915304205</v>
+        <v>-19.91943239356526</v>
       </c>
       <c r="F51">
-        <v>3.12214061655851</v>
+        <v>4.135389683254032</v>
       </c>
       <c r="G51">
-        <v>-5.17638008750938</v>
+        <v>-4.536299349673452</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.4907807291188922</v>
       </c>
       <c r="E52">
-        <v>-18.41249209803279</v>
+        <v>-19.00587163267986</v>
       </c>
       <c r="F52">
-        <v>2.896511560118786</v>
+        <v>4.113727875670825</v>
       </c>
       <c r="G52">
-        <v>-4.92014386276979</v>
+        <v>-5.048417570779931</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.322935678760278</v>
       </c>
       <c r="E53">
-        <v>-17.93429882824482</v>
+        <v>-17.58730450740708</v>
       </c>
       <c r="F53">
-        <v>2.678192017641365</v>
+        <v>3.78115824426449</v>
       </c>
       <c r="G53">
-        <v>-5.023681174510497</v>
+        <v>-5.687074774033971</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.1460568244523875</v>
       </c>
       <c r="E54">
-        <v>-16.97308946385072</v>
+        <v>-17.90850011182313</v>
       </c>
       <c r="F54">
-        <v>2.599695922552084</v>
+        <v>4.306025084556702</v>
       </c>
       <c r="G54">
-        <v>-5.559214884216239</v>
+        <v>-4.997325921472358</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.04261343765768077</v>
       </c>
       <c r="E55">
-        <v>-16.41763589901789</v>
+        <v>-16.02446472872394</v>
       </c>
       <c r="F55">
-        <v>3.256288090502668</v>
+        <v>4.623440562696222</v>
       </c>
       <c r="G55">
-        <v>-5.454717514269144</v>
+        <v>-6.587543160715734</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.2430267534749098</v>
       </c>
       <c r="E56">
-        <v>-16.12706183584172</v>
+        <v>-15.91429148459132</v>
       </c>
       <c r="F56">
-        <v>2.918759851823176</v>
+        <v>4.431113532583844</v>
       </c>
       <c r="G56">
-        <v>-6.072730155540289</v>
+        <v>-6.209025315392084</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.455463285108035</v>
       </c>
       <c r="E57">
-        <v>-15.65055768685861</v>
+        <v>-16.17089746423596</v>
       </c>
       <c r="F57">
-        <v>3.041177643343692</v>
+        <v>4.444065885294017</v>
       </c>
       <c r="G57">
-        <v>-6.32719192787083</v>
+        <v>-6.155123012921671</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.6772628359376642</v>
       </c>
       <c r="E58">
-        <v>-15.73500014167964</v>
+        <v>-15.69117357023341</v>
       </c>
       <c r="F58">
-        <v>3.079116870391909</v>
+        <v>4.105876609427091</v>
       </c>
       <c r="G58">
-        <v>-6.334720108427133</v>
+        <v>-6.644305774532078</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.904332568770863</v>
       </c>
       <c r="E59">
-        <v>-15.13316141758624</v>
+        <v>-14.99899178968698</v>
       </c>
       <c r="F59">
-        <v>2.985537861632455</v>
+        <v>4.255027473770753</v>
       </c>
       <c r="G59">
-        <v>-6.596090989298132</v>
+        <v>-6.496145619467534</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.132572192580725</v>
       </c>
       <c r="E60">
-        <v>-13.43660938687861</v>
+        <v>-14.69777581259278</v>
       </c>
       <c r="F60">
-        <v>2.825444263897811</v>
+        <v>4.03042227944089</v>
       </c>
       <c r="G60">
-        <v>-7.370242200383464</v>
+        <v>-7.007889748928075</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.354905742819436</v>
       </c>
       <c r="E61">
-        <v>-13.83467583757486</v>
+        <v>-14.71031968559403</v>
       </c>
       <c r="F61">
-        <v>3.097203444264634</v>
+        <v>4.148378484129928</v>
       </c>
       <c r="G61">
-        <v>-7.386109645153191</v>
+        <v>-7.219781216169127</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.566728145640944</v>
       </c>
       <c r="E62">
-        <v>-13.60237870640339</v>
+        <v>-13.47106654560297</v>
       </c>
       <c r="F62">
-        <v>2.75485742077046</v>
+        <v>3.997459883748692</v>
       </c>
       <c r="G62">
-        <v>-7.913486170650169</v>
+        <v>-7.362164469267642</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.760608744962599</v>
       </c>
       <c r="E63">
-        <v>-14.61463755828596</v>
+        <v>-13.36726486439916</v>
       </c>
       <c r="F63">
-        <v>2.837392635315791</v>
+        <v>4.110671199954495</v>
       </c>
       <c r="G63">
-        <v>-7.884071973533745</v>
+        <v>-7.958926718722205</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.932657704131109</v>
       </c>
       <c r="E64">
-        <v>-12.74248036250889</v>
+        <v>-12.96080715136669</v>
       </c>
       <c r="F64">
-        <v>2.594367863417278</v>
+        <v>3.663220263658314</v>
       </c>
       <c r="G64">
-        <v>-9.011812622032014</v>
+        <v>-8.244361955118167</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.078505701204623</v>
       </c>
       <c r="E65">
-        <v>-13.19748331690358</v>
+        <v>-13.03665456252116</v>
       </c>
       <c r="F65">
-        <v>2.469527925610976</v>
+        <v>3.815891689463874</v>
       </c>
       <c r="G65">
-        <v>-8.529704496239029</v>
+        <v>-7.820727995185329</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.196718721768712</v>
       </c>
       <c r="E66">
-        <v>-11.47104788621933</v>
+        <v>-13.39168239624851</v>
       </c>
       <c r="F66">
-        <v>2.280303959789484</v>
+        <v>3.435376152783504</v>
       </c>
       <c r="G66">
-        <v>-8.136401754536994</v>
+        <v>-7.899313725196549</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.286060902935322</v>
       </c>
       <c r="E67">
-        <v>-11.95158237706926</v>
+        <v>-12.62919605673301</v>
       </c>
       <c r="F67">
-        <v>2.437282896089602</v>
+        <v>3.409433342462629</v>
       </c>
       <c r="G67">
-        <v>-8.306189703609595</v>
+        <v>-8.302746736248753</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.345385708422036</v>
       </c>
       <c r="E68">
-        <v>-12.38381616415338</v>
+        <v>-12.03224808456789</v>
       </c>
       <c r="F68">
-        <v>2.3096911217712</v>
+        <v>3.599710991620481</v>
       </c>
       <c r="G68">
-        <v>-8.585977149315561</v>
+        <v>-8.436797346224923</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.373850043284522</v>
       </c>
       <c r="E69">
-        <v>-11.67496054231072</v>
+        <v>-12.40861861629339</v>
       </c>
       <c r="F69">
-        <v>1.619190562554421</v>
+        <v>3.468389907254676</v>
       </c>
       <c r="G69">
-        <v>-8.813395075135794</v>
+        <v>-9.326489907176358</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.368663302298123</v>
       </c>
       <c r="E70">
-        <v>-11.64682513330106</v>
+        <v>-11.51527296337824</v>
       </c>
       <c r="F70">
-        <v>1.900928256655367</v>
+        <v>3.604366416424214</v>
       </c>
       <c r="G70">
-        <v>-9.019456671682191</v>
+        <v>-8.308030366929431</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.328121737345841</v>
       </c>
       <c r="E71">
-        <v>-12.48053531200921</v>
+        <v>-11.88293071111298</v>
       </c>
       <c r="F71">
-        <v>1.946746914439013</v>
+        <v>3.211943926696005</v>
       </c>
       <c r="G71">
-        <v>-8.792962388067414</v>
+        <v>-8.362753684693583</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.249858882141427</v>
       </c>
       <c r="E72">
-        <v>-12.2624983454879</v>
+        <v>-13.03067244835703</v>
       </c>
       <c r="F72">
-        <v>1.888578955414432</v>
+        <v>3.026735886043285</v>
       </c>
       <c r="G72">
-        <v>-9.186427346500873</v>
+        <v>-8.168596809906406</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.13192801312639</v>
       </c>
       <c r="E73">
-        <v>-11.70879277162202</v>
+        <v>-12.37518489269476</v>
       </c>
       <c r="F73">
-        <v>1.70133147421602</v>
+        <v>2.949116203666166</v>
       </c>
       <c r="G73">
-        <v>-8.519044539602575</v>
+        <v>-8.053081944404617</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.972517093391061</v>
       </c>
       <c r="E74">
-        <v>-12.38867974523762</v>
+        <v>-12.46757481939926</v>
       </c>
       <c r="F74">
-        <v>1.531910459525854</v>
+        <v>2.829226589458994</v>
       </c>
       <c r="G74">
-        <v>-8.927330810415352</v>
+        <v>-7.725414078564173</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.769080989999528</v>
       </c>
       <c r="E75">
-        <v>-12.66924588085685</v>
+        <v>-13.26050608966833</v>
       </c>
       <c r="F75">
-        <v>1.560558717784273</v>
+        <v>3.237500717807175</v>
       </c>
       <c r="G75">
-        <v>-7.806178147540233</v>
+        <v>-7.785960645931904</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.523254561450072</v>
       </c>
       <c r="E76">
-        <v>-12.25013561144695</v>
+        <v>-13.39950307085976</v>
       </c>
       <c r="F76">
-        <v>1.611357520393549</v>
+        <v>2.712700146907187</v>
       </c>
       <c r="G76">
-        <v>-8.113244488489793</v>
+        <v>-7.757321116471669</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.237541317867704</v>
       </c>
       <c r="E77">
-        <v>-12.75039160660029</v>
+        <v>-14.00376000007325</v>
       </c>
       <c r="F77">
-        <v>1.125511754977611</v>
+        <v>2.880053556559966</v>
       </c>
       <c r="G77">
-        <v>-7.964091169763468</v>
+        <v>-7.237899831905558</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.9208849802449913</v>
       </c>
       <c r="E78">
-        <v>-13.44308057623557</v>
+        <v>-12.47046851429016</v>
       </c>
       <c r="F78">
-        <v>1.21701487502565</v>
+        <v>2.305027413293439</v>
       </c>
       <c r="G78">
-        <v>-7.96958005426758</v>
+        <v>-7.667343799259817</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.5823839203249213</v>
       </c>
       <c r="E79">
-        <v>-14.18079163445511</v>
+        <v>-14.01326073854135</v>
       </c>
       <c r="F79">
-        <v>1.472832953092999</v>
+        <v>2.550502495969433</v>
       </c>
       <c r="G79">
-        <v>-6.660954508049072</v>
+        <v>-7.07568310048127</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.2358996021314694</v>
       </c>
       <c r="E80">
-        <v>-14.67710785722178</v>
+        <v>-14.01679747674134</v>
       </c>
       <c r="F80">
-        <v>0.6461239418338982</v>
+        <v>2.473002098498317</v>
       </c>
       <c r="G80">
-        <v>-7.086200703659535</v>
+        <v>-6.19119140657203</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.1064211534353542</v>
       </c>
       <c r="E81">
-        <v>-15.61327928882747</v>
+        <v>-14.63002531296403</v>
       </c>
       <c r="F81">
-        <v>1.042996421249947</v>
+        <v>2.372998272162749</v>
       </c>
       <c r="G81">
-        <v>-6.399315472989392</v>
+        <v>-6.520385433906078</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.4329205361924989</v>
       </c>
       <c r="E82">
-        <v>-15.21107834136222</v>
+        <v>-15.24807144553088</v>
       </c>
       <c r="F82">
-        <v>1.191154901445055</v>
+        <v>2.334563681407658</v>
       </c>
       <c r="G82">
-        <v>-6.595561302011848</v>
+        <v>-6.145254276669103</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.7345068972823031</v>
       </c>
       <c r="E83">
-        <v>-16.14930117169338</v>
+        <v>-15.63355326695981</v>
       </c>
       <c r="F83">
-        <v>1.050824493206402</v>
+        <v>2.097927278919534</v>
       </c>
       <c r="G83">
-        <v>-5.802976973363855</v>
+        <v>-5.089921880205774</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.00696798517307</v>
       </c>
       <c r="E84">
-        <v>-17.05978709872757</v>
+        <v>-16.42878953049878</v>
       </c>
       <c r="F84">
-        <v>0.9370515439015014</v>
+        <v>2.165754001860758</v>
       </c>
       <c r="G84">
-        <v>-6.17970050300522</v>
+        <v>-5.164846146850559</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.247008340327743</v>
       </c>
       <c r="E85">
-        <v>-18.04471660997385</v>
+        <v>-17.77576148171029</v>
       </c>
       <c r="F85">
-        <v>0.8038235577744514</v>
+        <v>2.173237472977648</v>
       </c>
       <c r="G85">
-        <v>-5.787844469703846</v>
+        <v>-4.621155252936052</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.455601966501119</v>
       </c>
       <c r="E86">
-        <v>-19.96476694685605</v>
+        <v>-18.85988268762058</v>
       </c>
       <c r="F86">
-        <v>0.3030373578816214</v>
+        <v>1.756716118767195</v>
       </c>
       <c r="G86">
-        <v>-4.895913979967864</v>
+        <v>-4.333674099396821</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.631628606025658</v>
       </c>
       <c r="E87">
-        <v>-20.31993969175164</v>
+        <v>-20.06665761202863</v>
       </c>
       <c r="F87">
-        <v>0.827738524693273</v>
+        <v>1.698223439720717</v>
       </c>
       <c r="G87">
-        <v>-4.97247365610905</v>
+        <v>-4.850503226805682</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.775950811187597</v>
       </c>
       <c r="E88">
-        <v>-20.42355117704714</v>
+        <v>-20.21642783288431</v>
       </c>
       <c r="F88">
-        <v>0.6461098595880507</v>
+        <v>1.088656032492256</v>
       </c>
       <c r="G88">
-        <v>-4.990691588211659</v>
+        <v>-4.369904709778605</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.887154735549771</v>
       </c>
       <c r="E89">
-        <v>-22.49425478721651</v>
+        <v>-22.2342433951181</v>
       </c>
       <c r="F89">
-        <v>0.3784660084783359</v>
+        <v>1.266253033448053</v>
       </c>
       <c r="G89">
-        <v>-4.907639932267963</v>
+        <v>-4.415762386588589</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.964430597981083</v>
       </c>
       <c r="E90">
-        <v>-24.27818825237614</v>
+        <v>-23.71235542511774</v>
       </c>
       <c r="F90">
-        <v>0.3982333398113406</v>
+        <v>1.076725885157137</v>
       </c>
       <c r="G90">
-        <v>-4.692679589312006</v>
+        <v>-4.133697285551605</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.004826164643621</v>
       </c>
       <c r="E91">
-        <v>-25.91554859932952</v>
+        <v>-24.83421240493394</v>
       </c>
       <c r="F91">
-        <v>-0.0005327874875078343</v>
+        <v>0.838414523780553</v>
       </c>
       <c r="G91">
-        <v>-4.707355237687595</v>
+        <v>-4.463960619094838</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.004881142496759</v>
       </c>
       <c r="E92">
-        <v>-26.81253061687283</v>
+        <v>-26.73287928755192</v>
       </c>
       <c r="F92">
-        <v>0.2345645083662143</v>
+        <v>0.7483925246487196</v>
       </c>
       <c r="G92">
-        <v>-4.143652095988194</v>
+        <v>-4.087551591279704</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.960128392475727</v>
       </c>
       <c r="E93">
-        <v>-28.79293192685525</v>
+        <v>-28.18661454196826</v>
       </c>
       <c r="F93">
-        <v>-0.4208000190934202</v>
+        <v>0.2365898666660591</v>
       </c>
       <c r="G93">
-        <v>-4.375860381203753</v>
+        <v>-4.210412557333137</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.866420053240094</v>
       </c>
       <c r="E94">
-        <v>-31.23560439201466</v>
+        <v>-30.22450482947805</v>
       </c>
       <c r="F94">
-        <v>-0.4969700585156404</v>
+        <v>0.04336405792164356</v>
       </c>
       <c r="G94">
-        <v>-4.354686131934574</v>
+        <v>-4.192740865244507</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.72236278927279</v>
       </c>
       <c r="E95">
-        <v>-32.76022611431007</v>
+        <v>-32.22711830446809</v>
       </c>
       <c r="F95">
-        <v>-0.7338268067329086</v>
+        <v>-0.03814563777902218</v>
       </c>
       <c r="G95">
-        <v>-4.842564538602509</v>
+        <v>-4.208058759454715</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.523771825079375</v>
       </c>
       <c r="E96">
-        <v>-35.06145395807691</v>
+        <v>-34.21281113632847</v>
       </c>
       <c r="F96">
-        <v>-0.7434897124865648</v>
+        <v>-0.5050350435492963</v>
       </c>
       <c r="G96">
-        <v>-4.65605171346551</v>
+        <v>-3.794343193957534</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.278071741690734</v>
       </c>
       <c r="E97">
-        <v>-36.533339336316</v>
+        <v>-37.16963974760777</v>
       </c>
       <c r="F97">
-        <v>-1.291620422918998</v>
+        <v>-0.8493807459538284</v>
       </c>
       <c r="G97">
-        <v>-5.515260771091335</v>
+        <v>-4.574079295367616</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.9772966643890042</v>
       </c>
       <c r="E98">
-        <v>-39.32916258272658</v>
+        <v>-38.8873918293823</v>
       </c>
       <c r="F98">
-        <v>-1.693593160434083</v>
+        <v>-0.7674137914468173</v>
       </c>
       <c r="G98">
-        <v>-5.579429075279029</v>
+        <v>-5.090491294038528</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.6434108512631896</v>
       </c>
       <c r="E99">
-        <v>-42.70918161849668</v>
+        <v>-40.4849763248893</v>
       </c>
       <c r="F99">
-        <v>-1.548023328372723</v>
+        <v>-1.677610639764469</v>
       </c>
       <c r="G99">
-        <v>-5.584444551771025</v>
+        <v>-5.259964741284898</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.2535391046884802</v>
       </c>
       <c r="E100">
-        <v>-43.88394476014449</v>
+        <v>-43.8397853458587</v>
       </c>
       <c r="F100">
-        <v>-2.138940043527153</v>
+        <v>-1.640375525008632</v>
       </c>
       <c r="G100">
-        <v>-6.070207519839364</v>
+        <v>-5.371444051774317</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.1428325214394517</v>
       </c>
       <c r="E101">
-        <v>-45.3754384308368</v>
+        <v>-45.65792916790928</v>
       </c>
       <c r="F101">
-        <v>-2.113919206125594</v>
+        <v>-2.000610970933664</v>
       </c>
       <c r="G101">
-        <v>-5.736186717109059</v>
+        <v>-4.96329682387419</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.6203629530650644</v>
       </c>
       <c r="E102">
-        <v>-48.65253204512356</v>
+        <v>-48.45067984470566</v>
       </c>
       <c r="F102">
-        <v>-2.319699751226839</v>
+        <v>-2.275814502961327</v>
       </c>
       <c r="G102">
-        <v>-6.271803190453284</v>
+        <v>-5.515416366731682</v>
       </c>
     </row>
   </sheetData>
